--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484668_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484668_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6516</v>
+        <v>2.7726</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5421</v>
+        <v>3.6382</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8904</v>
+        <v>-0.8657</v>
       </c>
       <c r="G2" t="n">
         <v>4.1442</v>
@@ -610,13 +610,13 @@
         <v>1.8326</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.6879</v>
+        <v>-1.5669</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8258</v>
+        <v>-0.7296</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8621</v>
+        <v>-0.8373</v>
       </c>
       <c r="V2" t="n">
         <v>0.1953</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1586</v>
+        <v>-0.5433</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6946</v>
+        <v>1.31</v>
       </c>
       <c r="F4" t="n">
         <v>-1.8533</v>
@@ -766,10 +766,10 @@
         <v>1.8326</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.5581</v>
+        <v>-1.9427</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1666</v>
+        <v>-0.5513</v>
       </c>
       <c r="U4" t="n">
         <v>-1.3914</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.6232</v>
+        <v>-1.4775</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5492</v>
+        <v>-0.453</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.074</v>
+        <v>-1.0245</v>
       </c>
       <c r="G5" t="n">
         <v>-1.3523</v>
@@ -844,13 +844,13 @@
         <v>1.2828</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2317</v>
+        <v>-1.086</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.6746</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4609</v>
+        <v>-0.4114</v>
       </c>
       <c r="V5" t="n">
         <v>-0.3219</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. TORRES HERNANDO</t>
+          <t>J. BALFAGON MIRAVET</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.8935</v>
+        <v>-2.7061</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.8064</v>
+        <v>-0.6542</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0871</v>
+        <v>-2.0519</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.9986</v>
+        <v>-3.0537</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3284</v>
+        <v>-0.6594</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.327</v>
+        <v>-2.3942</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.9987</v>
+        <v>1.0559</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4305</v>
+        <v>0.8854</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.4292</v>
+        <v>0.1705</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.9999</v>
+        <v>-4.1095</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1021</v>
+        <v>-1.5448</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8977000000000001</v>
+        <v>-2.5647</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1991</v>
+        <v>1.4661</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1991</v>
+        <v>2.3823</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.9569</v>
+        <v>-1.43</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8077</v>
+        <v>-1.1157</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.1492</v>
+        <v>-0.3143</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1371</v>
+        <v>0.3115</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1371</v>
+        <v>-0.0104</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. BALFAGON MIRAVET</t>
+          <t>J. TORRES HERNANDO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.2172</v>
+        <v>-2.7507</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.19</v>
+        <v>-1.6141</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.0271</v>
+        <v>-1.1366</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.0537</v>
+        <v>-2.9986</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6594</v>
+        <v>0.3284</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.3942</v>
+        <v>-3.327</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0559</v>
+        <v>-0.9987</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8854</v>
+        <v>1.4305</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1705</v>
+        <v>-2.4292</v>
       </c>
       <c r="M7" t="n">
-        <v>-4.1095</v>
+        <v>-1.9999</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.5448</v>
+        <v>-1.1021</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.5647</v>
+        <v>-0.8977000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>1.4661</v>
+        <v>2.1991</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3823</v>
+        <v>2.1991</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.9411</v>
+        <v>-1.8141</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.6516</v>
+        <v>-0.6153999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2895</v>
+        <v>-1.1987</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3115</v>
+        <v>-0.1371</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.0104</v>
+        <v>-0.1371</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.2893</v>
+        <v>-2.8963</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.5875</v>
+        <v>-3.244</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2982</v>
+        <v>0.3477</v>
       </c>
       <c r="G8" t="n">
         <v>-3.707</v>
@@ -1078,13 +1078,13 @@
         <v>1.0995</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6819</v>
+        <v>-0.2888</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5324</v>
+        <v>-0.1889</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1495</v>
+        <v>-0.0999</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.5025</v>
+        <v>-3.332</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7193</v>
+        <v>-1.6231</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7833</v>
+        <v>-1.7089</v>
       </c>
       <c r="G9" t="n">
         <v>-1.6924</v>
@@ -1156,13 +1156,13 @@
         <v>0.733</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1782</v>
+        <v>-1.0077</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3303</v>
+        <v>-0.2342</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8479</v>
+        <v>-0.7736</v>
       </c>
       <c r="V9" t="n">
         <v>-0.4486</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.34</v>
+        <v>-4.7657</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1589</v>
+        <v>-0.5846</v>
       </c>
       <c r="F10" t="n">
         <v>-4.1812</v>
@@ -1234,10 +1234,10 @@
         <v>0.733</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2006</v>
+        <v>-0.2251</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2361</v>
+        <v>-0.1896</v>
       </c>
       <c r="U10" t="n">
         <v>-0.0355</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.079</v>
+        <v>-5.1755</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6026</v>
+        <v>-0.4514</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.4764</v>
+        <v>-4.7241</v>
       </c>
       <c r="G11" t="n">
         <v>-2.4713</v>
@@ -1312,13 +1312,13 @@
         <v>2.9321</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.7964</v>
+        <v>-1.8929</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2677</v>
+        <v>-1.1165</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5286999999999999</v>
+        <v>-0.7764</v>
       </c>
       <c r="V11" t="n">
         <v>-1.9109</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.2207</v>
+        <v>-5.3084</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.0923</v>
+        <v>-4.2296</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1283</v>
+        <v>-1.0788</v>
       </c>
       <c r="G12" t="n">
         <v>-5.0239</v>
@@ -1390,13 +1390,13 @@
         <v>2.0158</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.4707</v>
+        <v>-1.5584</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.497</v>
+        <v>-0.6342</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9738</v>
+        <v>-0.9242</v>
       </c>
       <c r="V12" t="n">
         <v>0.1744</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.8151</v>
+        <v>-6.0292</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.6188</v>
+        <v>-3.9072</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1963</v>
+        <v>-2.122</v>
       </c>
       <c r="G13" t="n">
         <v>-6.1331</v>
@@ -1468,13 +1468,13 @@
         <v>1.2828</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7212</v>
+        <v>-0.9353</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.46</v>
+        <v>-0.7485000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2612</v>
+        <v>-0.1869</v>
       </c>
       <c r="V13" t="n">
         <v>1.5889</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-31.8624</v>
+        <v>-31.587</v>
       </c>
       <c r="E14" t="n">
-        <v>-11.4632</v>
+        <v>-11.1879</v>
       </c>
       <c r="F14" t="n">
-        <v>-20.3992</v>
+        <v>-20.3993</v>
       </c>
       <c r="G14" t="n">
         <v>-25.7038</v>
@@ -1546,13 +1546,13 @@
         <v>18.3256</v>
       </c>
       <c r="S14" t="n">
-        <v>-14.0235</v>
+        <v>-13.7479</v>
       </c>
       <c r="T14" t="n">
-        <v>-7.0737</v>
+        <v>-6.798500000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-6.949699999999998</v>
+        <v>-6.949599999999999</v>
       </c>
       <c r="V14" t="n">
         <v>-1.2982</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>10.2473</v>
+        <v>10.6916</v>
       </c>
       <c r="E15" t="n">
-        <v>6.2571</v>
+        <v>7.1225</v>
       </c>
       <c r="F15" t="n">
-        <v>3.9902</v>
+        <v>3.5691</v>
       </c>
       <c r="G15" t="n">
         <v>8.9754</v>
@@ -1624,13 +1624,13 @@
         <v>0.9163</v>
       </c>
       <c r="S15" t="n">
-        <v>0.95</v>
+        <v>1.3942</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5324</v>
+        <v>0.333</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4824</v>
+        <v>1.0612</v>
       </c>
       <c r="V15" t="n">
         <v>0.3219</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.7245</v>
+        <v>5.0062</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8909</v>
+        <v>2.2179</v>
       </c>
       <c r="F16" t="n">
-        <v>2.8335</v>
+        <v>2.7883</v>
       </c>
       <c r="G16" t="n">
         <v>3.6221</v>
@@ -1702,13 +1702,13 @@
         <v>0.9163</v>
       </c>
       <c r="S16" t="n">
-        <v>3.0186</v>
+        <v>2.3003</v>
       </c>
       <c r="T16" t="n">
-        <v>2.1969</v>
+        <v>1.5238</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8218</v>
+        <v>0.7766</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.3949</v>
+        <v>4.6847</v>
       </c>
       <c r="E17" t="n">
-        <v>2.9799</v>
+        <v>3.3645</v>
       </c>
       <c r="F17" t="n">
-        <v>1.415</v>
+        <v>1.3202</v>
       </c>
       <c r="G17" t="n">
         <v>2.6152</v>
@@ -1780,13 +1780,13 @@
         <v>0.9163</v>
       </c>
       <c r="S17" t="n">
-        <v>1.429</v>
+        <v>1.7189</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1086</v>
+        <v>0.4932</v>
       </c>
       <c r="U17" t="n">
-        <v>1.3204</v>
+        <v>1.2256</v>
       </c>
       <c r="V17" t="n">
         <v>1.267</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>H. MARCO LOPEZ</t>
+          <t>E. CHOFRE TARREGA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.0957</v>
+        <v>4.5779</v>
       </c>
       <c r="E18" t="n">
-        <v>3.3082</v>
+        <v>4.0894</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7875</v>
+        <v>0.4885</v>
       </c>
       <c r="G18" t="n">
-        <v>1.4938</v>
+        <v>4.9087</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4004</v>
+        <v>-0.0092</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8941</v>
+        <v>4.9179</v>
       </c>
       <c r="J18" t="n">
-        <v>0.696</v>
+        <v>5.8983</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.8459</v>
+        <v>0.0184</v>
       </c>
       <c r="L18" t="n">
-        <v>1.5419</v>
+        <v>5.8799</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7977</v>
+        <v>-0.9896</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4456</v>
+        <v>-0.0276</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3522</v>
+        <v>-0.962</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3665</v>
+        <v>-2.3823</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9163</v>
+        <v>-3.6651</v>
       </c>
       <c r="R18" t="n">
         <v>1.2828</v>
       </c>
       <c r="S18" t="n">
-        <v>2.5366</v>
+        <v>2.062</v>
       </c>
       <c r="T18" t="n">
-        <v>2.5626</v>
+        <v>0.9008</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.026</v>
+        <v>1.1612</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3011</v>
+        <v>-0.0104</v>
       </c>
       <c r="W18" t="n">
-        <v>0.9658</v>
+        <v>0.9554</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.267</v>
+        <v>-0.9658</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. CHOFRE TARREGA</t>
+          <t>H. MARCO LOPEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.1749</v>
+        <v>3.3689</v>
       </c>
       <c r="E19" t="n">
-        <v>2.8394</v>
+        <v>1.9621</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3356</v>
+        <v>1.4069</v>
       </c>
       <c r="G19" t="n">
-        <v>4.9087</v>
+        <v>1.4938</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0092</v>
+        <v>-0.4004</v>
       </c>
       <c r="I19" t="n">
-        <v>4.9179</v>
+        <v>1.8941</v>
       </c>
       <c r="J19" t="n">
-        <v>5.8983</v>
+        <v>0.696</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0184</v>
+        <v>-0.8459</v>
       </c>
       <c r="L19" t="n">
-        <v>5.8799</v>
+        <v>1.5419</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9896</v>
+        <v>0.7977</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0276</v>
+        <v>0.4456</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.962</v>
+        <v>0.3522</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.3823</v>
+        <v>0.3665</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.6651</v>
+        <v>-0.9163</v>
       </c>
       <c r="R19" t="n">
         <v>1.2828</v>
       </c>
       <c r="S19" t="n">
-        <v>0.659</v>
+        <v>1.8098</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3492</v>
+        <v>1.2165</v>
       </c>
       <c r="U19" t="n">
-        <v>1.0082</v>
+        <v>0.5933</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.0104</v>
+        <v>-0.3011</v>
       </c>
       <c r="W19" t="n">
-        <v>0.9554</v>
+        <v>0.9658</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.9658</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. MELGAR GARCIA</t>
+          <t>J. ROIG MESA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.9666</v>
+        <v>1.5897</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0083</v>
+        <v>1.1163</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0417</v>
+        <v>0.4734</v>
       </c>
       <c r="G20" t="n">
-        <v>1.7091</v>
+        <v>1.3424</v>
       </c>
       <c r="H20" t="n">
-        <v>2.2703</v>
+        <v>0.4386</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5612</v>
+        <v>0.9038</v>
       </c>
       <c r="J20" t="n">
-        <v>2.32</v>
+        <v>2.6524</v>
       </c>
       <c r="K20" t="n">
-        <v>2.1116</v>
+        <v>1.2354</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2084</v>
+        <v>1.4169</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6109</v>
+        <v>-1.31</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1587</v>
+        <v>-0.7968</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7695</v>
+        <v>-0.5131</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.7489</v>
+        <v>0.1833</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.6651</v>
+        <v>-0.9163</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9163</v>
+        <v>1.0995</v>
       </c>
       <c r="S20" t="n">
-        <v>2.9959</v>
+        <v>0.9987</v>
       </c>
       <c r="T20" t="n">
-        <v>3.0211</v>
+        <v>0.3149</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0252</v>
+        <v>0.6838</v>
       </c>
       <c r="V20" t="n">
-        <v>0.0104</v>
+        <v>-0.9346</v>
       </c>
       <c r="W20" t="n">
-        <v>0.3324</v>
+        <v>-0.9346</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.1123</v>
+        <v>1.4692</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0824</v>
+        <v>-1.6017</v>
       </c>
       <c r="F21" t="n">
-        <v>3.1948</v>
+        <v>3.0709</v>
       </c>
       <c r="G21" t="n">
         <v>0.4393</v>
@@ -2092,13 +2092,13 @@
         <v>0.9163</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3224</v>
+        <v>0.6793</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6606</v>
+        <v>-0.1798</v>
       </c>
       <c r="U21" t="n">
-        <v>0.983</v>
+        <v>0.8591</v>
       </c>
       <c r="V21" t="n">
         <v>1.267</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. ROIG MESA</t>
+          <t>L. RODRIGUEZ CAMPIÑA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.0433</v>
+        <v>0.9502</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0202</v>
+        <v>0.9502</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0231</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>1.3424</v>
+        <v>0.9502</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4386</v>
+        <v>0.3251</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9038</v>
+        <v>0.6251</v>
       </c>
       <c r="J22" t="n">
-        <v>2.6524</v>
+        <v>0.9502</v>
       </c>
       <c r="K22" t="n">
-        <v>1.2354</v>
+        <v>0.3251</v>
       </c>
       <c r="L22" t="n">
-        <v>1.4169</v>
+        <v>0.6251</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.31</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7968</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5131</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1833</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.0995</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4523</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2187</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2335</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9346</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.9346</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ CAMPIÑA</t>
+          <t>A. MELGAR GARCIA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9502</v>
+        <v>0.8711</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9502</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>0.3051</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9502</v>
+        <v>1.7091</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3251</v>
+        <v>2.2703</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6251</v>
+        <v>-0.5612</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9502</v>
+        <v>2.32</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3251</v>
+        <v>2.1116</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6251</v>
+        <v>0.2084</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>-0.6109</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>0.1587</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>-0.7695</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-3.6651</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>0.9163</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.9005</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1.5788</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>0.3216</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.0104</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.3324</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.8475</v>
+        <v>-0.7063</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2273</v>
+        <v>0.612</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0749</v>
+        <v>-1.3182</v>
       </c>
       <c r="G24" t="n">
         <v>-0.3525</v>
@@ -2326,13 +2326,13 @@
         <v>0.9163</v>
       </c>
       <c r="S24" t="n">
-        <v>1.6595</v>
+        <v>1.8007</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3839</v>
+        <v>0.7685</v>
       </c>
       <c r="U24" t="n">
-        <v>1.2756</v>
+        <v>1.0322</v>
       </c>
       <c r="V24" t="n">
         <v>-0.3219</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>31.8622</v>
+        <v>32.5032</v>
       </c>
       <c r="E25" t="n">
-        <v>20.3991</v>
+        <v>20.3992</v>
       </c>
       <c r="F25" t="n">
-        <v>11.4631</v>
+        <v>12.1042</v>
       </c>
       <c r="G25" t="n">
         <v>25.7037</v>
@@ -2386,31 +2386,31 @@
         <v>15.0679</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.6296999999999999</v>
+        <v>-0.6297000000000001</v>
       </c>
       <c r="N25" t="n">
         <v>1.9375</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.567</v>
+        <v>-2.566999999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-9.162899999999999</v>
+        <v>-9.1629</v>
       </c>
       <c r="Q25" t="n">
         <v>-18.3258</v>
       </c>
       <c r="R25" t="n">
-        <v>9.1629</v>
+        <v>9.162899999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>14.0233</v>
+        <v>14.6644</v>
       </c>
       <c r="T25" t="n">
-        <v>6.949599999999999</v>
+        <v>6.9497</v>
       </c>
       <c r="U25" t="n">
-        <v>7.0737</v>
+        <v>7.714599999999999</v>
       </c>
       <c r="V25" t="n">
         <v>1.2983</v>
